--- a/artfynd/A 40508-2025 artfynd.xlsx
+++ b/artfynd/A 40508-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2051798</v>
+        <v>395049</v>
       </c>
       <c r="B2" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452517.4128398976</v>
+        <v>452446</v>
       </c>
       <c r="R2" t="n">
-        <v>7099488.586459038</v>
+        <v>7099265</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,21 +743,11 @@
           <t>2007-06-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-06-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>395051</v>
+        <v>395050</v>
       </c>
       <c r="B3" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452143.0359295897</v>
+        <v>452429</v>
       </c>
       <c r="R3" t="n">
-        <v>7099417.123781729</v>
+        <v>7099396</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +849,9 @@
           <t>2007-06-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-06-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>395050</v>
+        <v>395051</v>
       </c>
       <c r="B4" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452429.4805639302</v>
+        <v>452143</v>
       </c>
       <c r="R4" t="n">
-        <v>7099395.631103506</v>
+        <v>7099417</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -985,19 +955,9 @@
           <t>2007-06-30</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-06-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,6 +986,410 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1828476</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stortjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>452666</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7099396</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2007-06-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2007-06-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Sundström, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1883906</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stortjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>452680</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7099415</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2007-06-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2007-06-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Sundström, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2051798</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stortjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>452517</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7099489</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2007-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2007-06-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Sundström, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddare</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1930669</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stortjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>452665</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7099428</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hotagen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2007-06-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2007-06-30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Sundström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Sundström, * Naturskyddare</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Naturskyddare</t>
         </is>
